--- a/data/raw/01_FormatosRA_ReformaCurricular/FormatoRA_Esp.LogisGestCadAbast_PBOG.xlsx
+++ b/data/raw/01_FormatosRA_ReformaCurricular/FormatoRA_Esp.LogisGestCadAbast_PBOG.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://poligran-my.sharepoint.com/personal/micortes_poligran_edu_co/Documents/Escritorio/01_FormatosRA_ReformaCurricular/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5f15395a9ed9a48f/Proyectos_DS/Analisis_Curricular/data/raw/01_FormatosRA_ReformaCurricular/"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="697" documentId="8_{9D5C12F7-717D-4A89-AC5F-9AA3C543F7CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AC6AB34F-4B2F-4A1D-9D05-F16474DCC20C}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="3" activeTab="4" xr2:uid="{BD68381A-4EB3-42BA-ADD5-D7B5B6C7E498}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="3" activeTab="4" xr2:uid="{BD68381A-4EB3-42BA-ADD5-D7B5B6C7E498}"/>
   </bookViews>
   <sheets>
     <sheet name="Paso1 Analisis perfil egreso" sheetId="1" r:id="rId1"/>
@@ -3678,18 +3678,12 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -3707,14 +3701,14 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="14" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -3725,8 +3719,14 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -3743,6 +3743,18 @@
     <xf numFmtId="0" fontId="13" fillId="6" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -3755,17 +3767,11 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -3774,12 +3780,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -8515,23 +8515,23 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{46FA7EDF-246F-4EE0-BFE4-7EACACD45C48}">
   <dimension ref="A1:K22"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="76.26953125" defaultRowHeight="16.5" x14ac:dyDescent="0.5"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="76.21875" defaultRowHeight="18" x14ac:dyDescent="0.5"/>
   <cols>
-    <col min="1" max="1" width="19.7265625" style="3" customWidth="1"/>
-    <col min="2" max="2" width="16.7265625" style="3" customWidth="1"/>
+    <col min="1" max="1" width="19.77734375" style="3" customWidth="1"/>
+    <col min="2" max="2" width="16.77734375" style="3" customWidth="1"/>
     <col min="3" max="3" width="43" style="3" customWidth="1"/>
-    <col min="4" max="4" width="57.54296875" style="3" customWidth="1"/>
-    <col min="5" max="5" width="26.1796875" style="3" customWidth="1"/>
-    <col min="6" max="6" width="26.54296875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="30.26953125" style="1" customWidth="1"/>
+    <col min="4" max="4" width="57.5546875" style="3" customWidth="1"/>
+    <col min="5" max="5" width="26.21875" style="3" customWidth="1"/>
+    <col min="6" max="6" width="26.5546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="30.21875" style="1" customWidth="1"/>
     <col min="8" max="8" width="40" style="3" customWidth="1"/>
-    <col min="9" max="9" width="75.81640625" style="3" customWidth="1"/>
+    <col min="9" max="9" width="75.77734375" style="3" customWidth="1"/>
     <col min="10" max="10" width="30" style="3" customWidth="1"/>
-    <col min="11" max="11" width="53.26953125" style="3" customWidth="1"/>
-    <col min="12" max="16384" width="76.26953125" style="3"/>
+    <col min="11" max="11" width="53.21875" style="3" customWidth="1"/>
+    <col min="12" max="16384" width="76.21875" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="55.5" x14ac:dyDescent="0.5">
+    <row r="1" spans="1:11" ht="54" x14ac:dyDescent="0.5">
       <c r="A1" s="44" t="s">
         <v>0</v>
       </c>
@@ -8593,7 +8593,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="3" spans="1:11" s="6" customFormat="1" ht="123.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:11" s="6" customFormat="1" ht="123.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="93" t="s">
         <v>586</v>
       </c>
@@ -8628,7 +8628,7 @@
         <v>624</v>
       </c>
     </row>
-    <row r="4" spans="1:11" s="6" customFormat="1" ht="123.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:11" s="6" customFormat="1" ht="123.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="68"/>
       <c r="B4" s="68"/>
       <c r="C4" s="68"/>
@@ -8655,7 +8655,7 @@
       <c r="F5" s="28"/>
       <c r="G5" s="27"/>
     </row>
-    <row r="6" spans="1:11" s="5" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:11" s="5" customFormat="1" x14ac:dyDescent="0.3">
       <c r="E6" s="6"/>
       <c r="F6" s="6"/>
       <c r="G6" s="31"/>
@@ -8792,16 +8792,16 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{81C1850E-A9C8-4F69-8E80-DEAF9721FFBF}">
   <dimension ref="A1:G7"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.453125" defaultRowHeight="16.5" x14ac:dyDescent="0.5"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="18" x14ac:dyDescent="0.5"/>
   <cols>
     <col min="1" max="1" width="19" style="3" customWidth="1"/>
-    <col min="2" max="2" width="22.81640625" style="3" customWidth="1"/>
-    <col min="3" max="3" width="23.54296875" style="3" customWidth="1"/>
-    <col min="4" max="4" width="29.81640625" style="3" customWidth="1"/>
-    <col min="5" max="5" width="35.81640625" style="3" customWidth="1"/>
-    <col min="6" max="6" width="57.81640625" style="3" customWidth="1"/>
+    <col min="2" max="2" width="22.77734375" style="3" customWidth="1"/>
+    <col min="3" max="3" width="23.5546875" style="3" customWidth="1"/>
+    <col min="4" max="4" width="29.77734375" style="3" customWidth="1"/>
+    <col min="5" max="5" width="35.77734375" style="3" customWidth="1"/>
+    <col min="6" max="6" width="57.77734375" style="3" customWidth="1"/>
     <col min="7" max="7" width="39" style="3" customWidth="1"/>
-    <col min="8" max="16384" width="11.453125" style="3"/>
+    <col min="8" max="16384" width="11.44140625" style="3"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.5">
@@ -8815,7 +8815,7 @@
       <c r="F1" s="97"/>
       <c r="G1" s="97"/>
     </row>
-    <row r="2" spans="1:7" ht="52" x14ac:dyDescent="0.5">
+    <row r="2" spans="1:7" ht="48" x14ac:dyDescent="0.5">
       <c r="A2" s="54" t="s">
         <v>19</v>
       </c>
@@ -8838,7 +8838,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="3" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A3" s="57" t="s">
         <v>26</v>
       </c>
@@ -8861,7 +8861,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="4" spans="1:7" s="5" customFormat="1" ht="66" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:7" s="5" customFormat="1" ht="90" x14ac:dyDescent="0.3">
       <c r="A4" s="5">
         <v>1</v>
       </c>
@@ -8884,7 +8884,7 @@
         <v>590</v>
       </c>
     </row>
-    <row r="5" spans="1:7" s="5" customFormat="1" ht="66" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:7" s="5" customFormat="1" ht="72" x14ac:dyDescent="0.3">
       <c r="A5" s="5">
         <v>2</v>
       </c>
@@ -8935,22 +8935,22 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{94AAF649-42F4-466A-BE11-44357078F961}">
   <dimension ref="A1:I8"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.453125" defaultRowHeight="16.5" x14ac:dyDescent="0.5"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="18" x14ac:dyDescent="0.5"/>
   <cols>
-    <col min="1" max="1" width="81.1796875" style="6" customWidth="1"/>
-    <col min="2" max="2" width="16.7265625" style="7" customWidth="1"/>
-    <col min="3" max="3" width="19.1796875" style="6" customWidth="1"/>
-    <col min="4" max="4" width="35.81640625" style="6" customWidth="1"/>
-    <col min="5" max="5" width="17.54296875" style="6" customWidth="1"/>
-    <col min="6" max="6" width="17.81640625" style="6" customWidth="1"/>
-    <col min="7" max="7" width="20.1796875" style="8" customWidth="1"/>
-    <col min="8" max="8" width="18.26953125" style="1" customWidth="1"/>
+    <col min="1" max="1" width="81.21875" style="6" customWidth="1"/>
+    <col min="2" max="2" width="16.77734375" style="7" customWidth="1"/>
+    <col min="3" max="3" width="19.21875" style="6" customWidth="1"/>
+    <col min="4" max="4" width="35.77734375" style="6" customWidth="1"/>
+    <col min="5" max="5" width="17.5546875" style="6" customWidth="1"/>
+    <col min="6" max="6" width="17.77734375" style="6" customWidth="1"/>
+    <col min="7" max="7" width="20.21875" style="8" customWidth="1"/>
+    <col min="8" max="8" width="18.21875" style="1" customWidth="1"/>
     <col min="9" max="9" width="72" style="1" customWidth="1"/>
-    <col min="10" max="10" width="43.26953125" style="6" customWidth="1"/>
-    <col min="11" max="16384" width="11.453125" style="6"/>
+    <col min="10" max="10" width="43.21875" style="6" customWidth="1"/>
+    <col min="11" max="16384" width="11.44140625" style="6"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="78" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:9" ht="84" x14ac:dyDescent="0.3">
       <c r="A1" s="44" t="s">
         <v>33</v>
       </c>
@@ -8979,7 +8979,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="2" spans="1:9" ht="33.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:9" ht="36.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A2" s="48" t="s">
         <v>42</v>
       </c>
@@ -9008,7 +9008,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="3" spans="1:9" ht="49.5" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:9" ht="54" x14ac:dyDescent="0.3">
       <c r="A3" s="40" t="s">
         <v>637</v>
       </c>
@@ -9037,7 +9037,7 @@
         <v>593</v>
       </c>
     </row>
-    <row r="4" spans="1:9" ht="49.5" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:9" ht="54" x14ac:dyDescent="0.3">
       <c r="A4" s="41" t="s">
         <v>637</v>
       </c>
@@ -9066,7 +9066,7 @@
         <v>629</v>
       </c>
     </row>
-    <row r="5" spans="1:9" ht="50" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:9" ht="54.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A5" s="41" t="s">
         <v>637</v>
       </c>
@@ -9095,7 +9095,7 @@
         <v>630</v>
       </c>
     </row>
-    <row r="6" spans="1:9" ht="49.5" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:9" ht="54" x14ac:dyDescent="0.3">
       <c r="A6" s="40" t="s">
         <v>628</v>
       </c>
@@ -9124,7 +9124,7 @@
         <v>593</v>
       </c>
     </row>
-    <row r="7" spans="1:9" ht="49.5" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:9" ht="54" x14ac:dyDescent="0.3">
       <c r="A7" s="41" t="s">
         <v>628</v>
       </c>
@@ -9153,7 +9153,7 @@
         <v>631</v>
       </c>
     </row>
-    <row r="8" spans="1:9" ht="50" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:9" ht="54.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A8" s="43" t="s">
         <v>628</v>
       </c>
@@ -9216,18 +9216,18 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1F726B80-E6B4-4ED4-A764-E59AF4E18393}">
   <dimension ref="A1:F22"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.453125" defaultRowHeight="16.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="18" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="46.26953125" style="31" customWidth="1"/>
-    <col min="2" max="2" width="43.81640625" style="8" customWidth="1"/>
+    <col min="1" max="1" width="46.21875" style="31" customWidth="1"/>
+    <col min="2" max="2" width="43.77734375" style="8" customWidth="1"/>
     <col min="3" max="3" width="48" style="5" customWidth="1"/>
-    <col min="4" max="4" width="45.81640625" style="31" customWidth="1"/>
-    <col min="5" max="5" width="39.1796875" style="31" customWidth="1"/>
-    <col min="6" max="6" width="33.453125" style="31" customWidth="1"/>
-    <col min="7" max="16384" width="11.453125" style="31"/>
+    <col min="4" max="4" width="45.77734375" style="31" customWidth="1"/>
+    <col min="5" max="5" width="39.21875" style="31" customWidth="1"/>
+    <col min="6" max="6" width="33.44140625" style="31" customWidth="1"/>
+    <col min="7" max="16384" width="11.44140625" style="31"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="65" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:6" ht="60" x14ac:dyDescent="0.3">
       <c r="A1" s="44" t="s">
         <v>51</v>
       </c>
@@ -9247,7 +9247,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="2" spans="1:6" ht="33" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:6" ht="36" x14ac:dyDescent="0.3">
       <c r="A2" s="48" t="s">
         <v>57</v>
       </c>
@@ -9267,14 +9267,14 @@
         <v>62</v>
       </c>
     </row>
-    <row r="3" spans="1:6" ht="82.5" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:6" ht="90" x14ac:dyDescent="0.3">
       <c r="A3" s="63" t="s">
         <v>593</v>
       </c>
-      <c r="B3" s="104" t="s">
+      <c r="B3" s="98" t="s">
         <v>632</v>
       </c>
-      <c r="C3" s="105" t="s">
+      <c r="C3" s="99" t="s">
         <v>618</v>
       </c>
       <c r="D3" s="64" t="s">
@@ -9287,12 +9287,12 @@
         <v>65</v>
       </c>
     </row>
-    <row r="4" spans="1:6" ht="82.5" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:6" ht="90" x14ac:dyDescent="0.3">
       <c r="A4" s="5" t="s">
         <v>629</v>
       </c>
       <c r="B4" s="74"/>
-      <c r="C4" s="102"/>
+      <c r="C4" s="100"/>
       <c r="D4" s="32" t="s">
         <v>66</v>
       </c>
@@ -9300,12 +9300,12 @@
         <v>67</v>
       </c>
     </row>
-    <row r="5" spans="1:6" ht="66" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:6" ht="72" x14ac:dyDescent="0.3">
       <c r="A5" s="5" t="s">
         <v>630</v>
       </c>
       <c r="B5" s="74"/>
-      <c r="C5" s="102"/>
+      <c r="C5" s="100"/>
       <c r="D5" s="32" t="s">
         <v>68</v>
       </c>
@@ -9313,24 +9313,24 @@
         <v>69</v>
       </c>
     </row>
-    <row r="6" spans="1:6" ht="66.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:6" ht="72.599999999999994" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A6" s="34" t="s">
         <v>631</v>
       </c>
       <c r="B6" s="75"/>
-      <c r="C6" s="103"/>
+      <c r="C6" s="101"/>
       <c r="D6" s="61"/>
       <c r="E6" s="38"/>
       <c r="F6" s="38"/>
     </row>
-    <row r="7" spans="1:6" ht="82.5" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:6" ht="90" x14ac:dyDescent="0.3">
       <c r="A7" s="5" t="s">
         <v>593</v>
       </c>
       <c r="B7" s="74" t="s">
         <v>633</v>
       </c>
-      <c r="C7" s="102" t="s">
+      <c r="C7" s="100" t="s">
         <v>634</v>
       </c>
       <c r="D7" s="32" t="s">
@@ -9343,12 +9343,12 @@
         <v>65</v>
       </c>
     </row>
-    <row r="8" spans="1:6" ht="82.5" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:6" ht="90" x14ac:dyDescent="0.3">
       <c r="A8" s="5" t="s">
         <v>629</v>
       </c>
       <c r="B8" s="74"/>
-      <c r="C8" s="102"/>
+      <c r="C8" s="100"/>
       <c r="D8" s="32" t="s">
         <v>71</v>
       </c>
@@ -9356,33 +9356,33 @@
         <v>67</v>
       </c>
     </row>
-    <row r="9" spans="1:6" ht="66" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:6" ht="72" x14ac:dyDescent="0.3">
       <c r="A9" s="5" t="s">
         <v>630</v>
       </c>
       <c r="B9" s="74"/>
-      <c r="C9" s="102"/>
+      <c r="C9" s="100"/>
       <c r="D9" s="32" t="s">
         <v>68</v>
       </c>
       <c r="F9" s="5"/>
     </row>
-    <row r="10" spans="1:6" ht="66.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:6" ht="72.599999999999994" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A10" s="5" t="s">
         <v>631</v>
       </c>
       <c r="B10" s="74"/>
-      <c r="C10" s="102"/>
+      <c r="C10" s="100"/>
       <c r="D10" s="32"/>
     </row>
-    <row r="11" spans="1:6" ht="82.5" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:6" ht="90" x14ac:dyDescent="0.3">
       <c r="A11" s="35" t="s">
         <v>593</v>
       </c>
       <c r="B11" s="73" t="s">
         <v>614</v>
       </c>
-      <c r="C11" s="101" t="s">
+      <c r="C11" s="105" t="s">
         <v>654</v>
       </c>
       <c r="D11" s="60" t="s">
@@ -9395,12 +9395,12 @@
         <v>65</v>
       </c>
     </row>
-    <row r="12" spans="1:6" ht="82.5" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:6" ht="90" x14ac:dyDescent="0.3">
       <c r="A12" s="5" t="s">
         <v>629</v>
       </c>
       <c r="B12" s="74"/>
-      <c r="C12" s="102"/>
+      <c r="C12" s="100"/>
       <c r="D12" s="32" t="s">
         <v>71</v>
       </c>
@@ -9408,12 +9408,12 @@
         <v>67</v>
       </c>
     </row>
-    <row r="13" spans="1:6" ht="66" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:6" ht="72" x14ac:dyDescent="0.3">
       <c r="A13" s="5" t="s">
         <v>630</v>
       </c>
       <c r="B13" s="74"/>
-      <c r="C13" s="102"/>
+      <c r="C13" s="100"/>
       <c r="D13" s="32" t="s">
         <v>68</v>
       </c>
@@ -9421,24 +9421,24 @@
         <v>69</v>
       </c>
     </row>
-    <row r="14" spans="1:6" ht="66.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:6" ht="72.599999999999994" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A14" s="34" t="s">
         <v>631</v>
       </c>
       <c r="B14" s="75"/>
-      <c r="C14" s="103"/>
+      <c r="C14" s="101"/>
       <c r="D14" s="61"/>
       <c r="E14" s="38"/>
       <c r="F14" s="38"/>
     </row>
-    <row r="15" spans="1:6" ht="82.5" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:6" ht="90" x14ac:dyDescent="0.3">
       <c r="A15" s="5" t="s">
         <v>593</v>
       </c>
-      <c r="B15" s="98" t="s">
+      <c r="B15" s="102" t="s">
         <v>616</v>
       </c>
-      <c r="C15" s="90" t="s">
+      <c r="C15" s="88" t="s">
         <v>635</v>
       </c>
       <c r="D15" s="32" t="s">
@@ -9451,12 +9451,12 @@
         <v>65</v>
       </c>
     </row>
-    <row r="16" spans="1:6" ht="82.5" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:6" ht="90" x14ac:dyDescent="0.3">
       <c r="A16" s="5" t="s">
         <v>629</v>
       </c>
-      <c r="B16" s="98"/>
-      <c r="C16" s="90"/>
+      <c r="B16" s="102"/>
+      <c r="C16" s="88"/>
       <c r="D16" s="32" t="s">
         <v>66</v>
       </c>
@@ -9464,12 +9464,12 @@
         <v>67</v>
       </c>
     </row>
-    <row r="17" spans="1:6" ht="66" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:6" ht="72" x14ac:dyDescent="0.3">
       <c r="A17" s="5" t="s">
         <v>630</v>
       </c>
-      <c r="B17" s="98"/>
-      <c r="C17" s="90"/>
+      <c r="B17" s="102"/>
+      <c r="C17" s="88"/>
       <c r="D17" s="32" t="s">
         <v>68</v>
       </c>
@@ -9477,24 +9477,24 @@
         <v>69</v>
       </c>
     </row>
-    <row r="18" spans="1:6" ht="66.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:6" ht="72.599999999999994" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A18" s="34" t="s">
         <v>631</v>
       </c>
-      <c r="B18" s="99"/>
-      <c r="C18" s="91"/>
+      <c r="B18" s="103"/>
+      <c r="C18" s="89"/>
       <c r="D18" s="38"/>
       <c r="E18" s="38"/>
       <c r="F18" s="38"/>
     </row>
-    <row r="19" spans="1:6" ht="82.5" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:6" ht="90" x14ac:dyDescent="0.3">
       <c r="A19" s="5" t="s">
         <v>593</v>
       </c>
-      <c r="B19" s="100" t="s">
+      <c r="B19" s="104" t="s">
         <v>615</v>
       </c>
-      <c r="C19" s="89" t="s">
+      <c r="C19" s="87" t="s">
         <v>619</v>
       </c>
       <c r="D19" s="32" t="s">
@@ -9507,12 +9507,12 @@
         <v>65</v>
       </c>
     </row>
-    <row r="20" spans="1:6" ht="82.5" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:6" ht="90" x14ac:dyDescent="0.3">
       <c r="A20" s="5" t="s">
         <v>629</v>
       </c>
-      <c r="B20" s="98"/>
-      <c r="C20" s="90"/>
+      <c r="B20" s="102"/>
+      <c r="C20" s="88"/>
       <c r="D20" s="32" t="s">
         <v>66</v>
       </c>
@@ -9520,12 +9520,12 @@
         <v>67</v>
       </c>
     </row>
-    <row r="21" spans="1:6" ht="66" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:6" ht="72" x14ac:dyDescent="0.3">
       <c r="A21" s="5" t="s">
         <v>630</v>
       </c>
-      <c r="B21" s="98"/>
-      <c r="C21" s="90"/>
+      <c r="B21" s="102"/>
+      <c r="C21" s="88"/>
       <c r="D21" s="32" t="s">
         <v>68</v>
       </c>
@@ -9533,28 +9533,28 @@
         <v>69</v>
       </c>
     </row>
-    <row r="22" spans="1:6" ht="66.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:6" ht="72.599999999999994" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A22" s="34" t="s">
         <v>631</v>
       </c>
-      <c r="B22" s="99"/>
-      <c r="C22" s="91"/>
+      <c r="B22" s="103"/>
+      <c r="C22" s="89"/>
       <c r="D22" s="38"/>
       <c r="E22" s="38"/>
       <c r="F22" s="38"/>
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="B19:B22"/>
+    <mergeCell ref="C19:C22"/>
+    <mergeCell ref="C15:C18"/>
+    <mergeCell ref="B11:B14"/>
+    <mergeCell ref="C11:C14"/>
     <mergeCell ref="B3:B6"/>
     <mergeCell ref="C3:C6"/>
     <mergeCell ref="B7:B10"/>
     <mergeCell ref="C7:C10"/>
     <mergeCell ref="B15:B18"/>
-    <mergeCell ref="B19:B22"/>
-    <mergeCell ref="C19:C22"/>
-    <mergeCell ref="C15:C18"/>
-    <mergeCell ref="B11:B14"/>
-    <mergeCell ref="C11:C14"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A3:A22" xr:uid="{D048ED25-334D-4F32-B2A7-D11385F03FF6}">
@@ -9570,28 +9570,28 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1B248250-C92C-4D02-A0C3-2CB27C341894}">
   <dimension ref="A1:Q43"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.453125" defaultRowHeight="16.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="18" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="11.1796875" style="5" customWidth="1"/>
+    <col min="1" max="1" width="11.21875" style="5" customWidth="1"/>
     <col min="2" max="2" width="57" style="5" customWidth="1"/>
-    <col min="3" max="3" width="17.26953125" style="5" customWidth="1"/>
-    <col min="4" max="4" width="26.54296875" style="5" customWidth="1"/>
-    <col min="5" max="5" width="49.54296875" style="6" customWidth="1"/>
-    <col min="6" max="6" width="27.1796875" style="7" customWidth="1"/>
-    <col min="7" max="7" width="16.7265625" style="7" customWidth="1"/>
-    <col min="8" max="8" width="18.1796875" style="7" customWidth="1"/>
-    <col min="9" max="9" width="13.54296875" style="7" customWidth="1"/>
-    <col min="10" max="10" width="20.453125" style="7" customWidth="1"/>
-    <col min="11" max="11" width="24.453125" style="7" customWidth="1"/>
-    <col min="12" max="12" width="11.26953125" style="7" customWidth="1"/>
-    <col min="13" max="13" width="33.26953125" style="6" customWidth="1"/>
-    <col min="14" max="14" width="60.7265625" style="6" customWidth="1"/>
-    <col min="15" max="15" width="58.1796875" style="6" customWidth="1"/>
-    <col min="16" max="16" width="104.54296875" style="6" customWidth="1"/>
-    <col min="17" max="16384" width="11.453125" style="5"/>
+    <col min="3" max="3" width="17.21875" style="5" customWidth="1"/>
+    <col min="4" max="4" width="26.5546875" style="5" customWidth="1"/>
+    <col min="5" max="5" width="49.5546875" style="6" customWidth="1"/>
+    <col min="6" max="6" width="27.21875" style="7" customWidth="1"/>
+    <col min="7" max="7" width="16.77734375" style="7" customWidth="1"/>
+    <col min="8" max="8" width="18.21875" style="7" customWidth="1"/>
+    <col min="9" max="9" width="13.5546875" style="7" customWidth="1"/>
+    <col min="10" max="10" width="20.44140625" style="7" customWidth="1"/>
+    <col min="11" max="11" width="24.44140625" style="7" customWidth="1"/>
+    <col min="12" max="12" width="11.21875" style="7" customWidth="1"/>
+    <col min="13" max="13" width="33.21875" style="6" customWidth="1"/>
+    <col min="14" max="14" width="60.77734375" style="6" customWidth="1"/>
+    <col min="15" max="15" width="58.21875" style="6" customWidth="1"/>
+    <col min="16" max="16" width="104.5546875" style="6" customWidth="1"/>
+    <col min="17" max="16384" width="11.44140625" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" s="7" customFormat="1" ht="65" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:17" s="7" customFormat="1" ht="60" x14ac:dyDescent="0.3">
       <c r="A1" s="44" t="s">
         <v>72</v>
       </c>
@@ -9610,10 +9610,10 @@
       <c r="F1" s="44" t="s">
         <v>77</v>
       </c>
-      <c r="G1" s="86" t="s">
+      <c r="G1" s="85" t="s">
         <v>78</v>
       </c>
-      <c r="H1" s="87"/>
+      <c r="H1" s="86"/>
       <c r="I1" s="44" t="s">
         <v>79</v>
       </c>
@@ -9639,7 +9639,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="2" spans="1:17" s="7" customFormat="1" ht="33" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:17" s="7" customFormat="1" ht="36" x14ac:dyDescent="0.3">
       <c r="A2" s="48" t="s">
         <v>87</v>
       </c>
@@ -9689,7 +9689,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="3" spans="1:17" ht="66" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:17" ht="72" x14ac:dyDescent="0.3">
       <c r="A3" s="5" t="str">
         <f>_xlfn.XLOOKUP(B3,'Paso 3 Redacción RA '!I$3:I$8,'Paso 3 Redacción RA '!C$3:C$8,,0,1)</f>
         <v>Saber</v>
@@ -9728,23 +9728,23 @@
         <f>SUM(J3:K5)</f>
         <v>96</v>
       </c>
-      <c r="M3" s="85" t="s">
+      <c r="M3" s="83" t="s">
         <v>611</v>
       </c>
-      <c r="N3" s="85" t="s">
+      <c r="N3" s="83" t="s">
         <v>650</v>
       </c>
-      <c r="O3" s="80" t="s">
+      <c r="O3" s="77" t="s">
         <v>617</v>
       </c>
-      <c r="P3" s="85" t="s">
+      <c r="P3" s="83" t="s">
         <v>100</v>
       </c>
       <c r="Q3" s="5" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="4" spans="1:17" ht="66" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:17" ht="72" x14ac:dyDescent="0.3">
       <c r="A4" s="5" t="str">
         <f>_xlfn.XLOOKUP(B4,'Paso 3 Redacción RA '!I$3:I$8,'Paso 3 Redacción RA '!C$3:C$8,,0,1)</f>
         <v>Saberhacer</v>
@@ -9762,12 +9762,12 @@
       <c r="J4" s="74"/>
       <c r="K4" s="74"/>
       <c r="L4" s="74"/>
-      <c r="M4" s="85"/>
-      <c r="N4" s="85"/>
-      <c r="O4" s="80"/>
-      <c r="P4" s="85"/>
-    </row>
-    <row r="5" spans="1:17" ht="50" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="M4" s="83"/>
+      <c r="N4" s="83"/>
+      <c r="O4" s="77"/>
+      <c r="P4" s="83"/>
+    </row>
+    <row r="5" spans="1:17" ht="54.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A5" s="34" t="str">
         <f>_xlfn.XLOOKUP(B5,'Paso 3 Redacción RA '!I$3:I$8,'Paso 3 Redacción RA '!C$3:C$8,,0,1)</f>
         <v>Saberser</v>
@@ -9785,12 +9785,12 @@
       <c r="J5" s="75"/>
       <c r="K5" s="75"/>
       <c r="L5" s="75"/>
-      <c r="M5" s="92"/>
-      <c r="N5" s="92"/>
-      <c r="O5" s="88"/>
-      <c r="P5" s="92"/>
-    </row>
-    <row r="6" spans="1:17" ht="66" x14ac:dyDescent="0.35">
+      <c r="M5" s="84"/>
+      <c r="N5" s="84"/>
+      <c r="O5" s="78"/>
+      <c r="P5" s="84"/>
+    </row>
+    <row r="6" spans="1:17" ht="72" x14ac:dyDescent="0.3">
       <c r="A6" s="35" t="str">
         <f>_xlfn.XLOOKUP(B6,'Paso 3 Redacción RA '!I$3:I$8,'Paso 3 Redacción RA '!C$3:C$8,,0,1)</f>
         <v>Saber</v>
@@ -9804,7 +9804,7 @@
       <c r="D6" s="67" t="s">
         <v>596</v>
       </c>
-      <c r="E6" s="89" t="s">
+      <c r="E6" s="87" t="s">
         <v>638</v>
       </c>
       <c r="F6" s="67" t="s">
@@ -9829,20 +9829,20 @@
         <f>SUM(J6:K9)</f>
         <v>96</v>
       </c>
-      <c r="M6" s="84" t="s">
+      <c r="M6" s="82" t="s">
         <v>612</v>
       </c>
-      <c r="N6" s="84" t="s">
+      <c r="N6" s="82" t="s">
         <v>651</v>
       </c>
-      <c r="O6" s="79" t="s">
+      <c r="O6" s="76" t="s">
         <v>617</v>
       </c>
-      <c r="P6" s="84" t="s">
+      <c r="P6" s="82" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="7" spans="1:17" ht="66" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:17" ht="72" x14ac:dyDescent="0.3">
       <c r="A7" s="5" t="str">
         <f>_xlfn.XLOOKUP(B7,'Paso 3 Redacción RA '!I$3:I$8,'Paso 3 Redacción RA '!C$3:C$8,,0,1)</f>
         <v>Saberhacer</v>
@@ -9852,7 +9852,7 @@
       </c>
       <c r="C7" s="68"/>
       <c r="D7" s="68"/>
-      <c r="E7" s="90"/>
+      <c r="E7" s="88"/>
       <c r="F7" s="68"/>
       <c r="G7" s="74"/>
       <c r="H7" s="74"/>
@@ -9860,12 +9860,12 @@
       <c r="J7" s="74"/>
       <c r="K7" s="74"/>
       <c r="L7" s="74"/>
-      <c r="M7" s="85"/>
-      <c r="N7" s="85"/>
-      <c r="O7" s="80"/>
-      <c r="P7" s="85"/>
-    </row>
-    <row r="8" spans="1:17" ht="49.5" x14ac:dyDescent="0.35">
+      <c r="M7" s="83"/>
+      <c r="N7" s="83"/>
+      <c r="O7" s="77"/>
+      <c r="P7" s="83"/>
+    </row>
+    <row r="8" spans="1:17" ht="54" x14ac:dyDescent="0.3">
       <c r="A8" s="5" t="str">
         <f>_xlfn.XLOOKUP(B8,'Paso 3 Redacción RA '!I$3:I$8,'Paso 3 Redacción RA '!C$3:C$8,,0,1)</f>
         <v>Saberhacer</v>
@@ -9875,7 +9875,7 @@
       </c>
       <c r="C8" s="68"/>
       <c r="D8" s="68"/>
-      <c r="E8" s="90"/>
+      <c r="E8" s="88"/>
       <c r="F8" s="68"/>
       <c r="G8" s="74"/>
       <c r="H8" s="74"/>
@@ -9883,12 +9883,12 @@
       <c r="J8" s="74"/>
       <c r="K8" s="74"/>
       <c r="L8" s="74"/>
-      <c r="M8" s="85"/>
-      <c r="N8" s="85"/>
-      <c r="O8" s="80"/>
-      <c r="P8" s="85"/>
-    </row>
-    <row r="9" spans="1:17" ht="50" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="M8" s="83"/>
+      <c r="N8" s="83"/>
+      <c r="O8" s="77"/>
+      <c r="P8" s="83"/>
+    </row>
+    <row r="9" spans="1:17" ht="54.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A9" s="34" t="str">
         <f>_xlfn.XLOOKUP(B9,'Paso 3 Redacción RA '!I$3:I$8,'Paso 3 Redacción RA '!C$3:C$8,,0,1)</f>
         <v>Saberser</v>
@@ -9898,7 +9898,7 @@
       </c>
       <c r="C9" s="69"/>
       <c r="D9" s="69"/>
-      <c r="E9" s="91"/>
+      <c r="E9" s="89"/>
       <c r="F9" s="69"/>
       <c r="G9" s="75"/>
       <c r="H9" s="75"/>
@@ -9906,12 +9906,12 @@
       <c r="J9" s="75"/>
       <c r="K9" s="75"/>
       <c r="L9" s="75"/>
-      <c r="M9" s="92"/>
-      <c r="N9" s="92"/>
-      <c r="O9" s="88"/>
-      <c r="P9" s="92"/>
-    </row>
-    <row r="10" spans="1:17" ht="66" x14ac:dyDescent="0.35">
+      <c r="M9" s="84"/>
+      <c r="N9" s="84"/>
+      <c r="O9" s="78"/>
+      <c r="P9" s="84"/>
+    </row>
+    <row r="10" spans="1:17" ht="72" x14ac:dyDescent="0.3">
       <c r="A10" s="5" t="str">
         <f>_xlfn.XLOOKUP(B10,'Paso 3 Redacción RA '!I$3:I$8,'Paso 3 Redacción RA '!C$3:C$8,,0,1)</f>
         <v>Saber</v>
@@ -9950,20 +9950,20 @@
         <f>SUM(J10:K10)</f>
         <v>96</v>
       </c>
-      <c r="M10" s="79" t="s">
+      <c r="M10" s="76" t="s">
         <v>645</v>
       </c>
-      <c r="N10" s="84" t="s">
+      <c r="N10" s="82" t="s">
         <v>650</v>
       </c>
-      <c r="O10" s="79" t="s">
+      <c r="O10" s="76" t="s">
         <v>617</v>
       </c>
-      <c r="P10" s="84" t="s">
+      <c r="P10" s="82" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="11" spans="1:17" ht="66" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:17" ht="72" x14ac:dyDescent="0.3">
       <c r="A11" s="5" t="str">
         <f>_xlfn.XLOOKUP(B11,'Paso 3 Redacción RA '!I$3:I$8,'Paso 3 Redacción RA '!C$3:C$8,,0,1)</f>
         <v>Saberhacer</v>
@@ -9981,12 +9981,12 @@
       <c r="J11" s="74"/>
       <c r="K11" s="74"/>
       <c r="L11" s="74"/>
-      <c r="M11" s="80"/>
-      <c r="N11" s="85"/>
-      <c r="O11" s="80"/>
-      <c r="P11" s="85"/>
-    </row>
-    <row r="12" spans="1:17" ht="50" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="M11" s="77"/>
+      <c r="N11" s="83"/>
+      <c r="O11" s="77"/>
+      <c r="P11" s="83"/>
+    </row>
+    <row r="12" spans="1:17" ht="54.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A12" s="34" t="str">
         <f>_xlfn.XLOOKUP(B12,'Paso 3 Redacción RA '!I$3:I$8,'Paso 3 Redacción RA '!C$3:C$8,,0,1)</f>
         <v>Saberser</v>
@@ -10004,12 +10004,12 @@
       <c r="J12" s="74"/>
       <c r="K12" s="74"/>
       <c r="L12" s="74"/>
-      <c r="M12" s="80"/>
-      <c r="N12" s="85"/>
-      <c r="O12" s="80"/>
-      <c r="P12" s="85"/>
-    </row>
-    <row r="13" spans="1:17" ht="66" x14ac:dyDescent="0.35">
+      <c r="M12" s="77"/>
+      <c r="N12" s="83"/>
+      <c r="O12" s="77"/>
+      <c r="P12" s="83"/>
+    </row>
+    <row r="13" spans="1:17" ht="72" x14ac:dyDescent="0.3">
       <c r="A13" s="5" t="str">
         <f>_xlfn.XLOOKUP(B13,'Paso 3 Redacción RA '!I$3:I$8,'Paso 3 Redacción RA '!C$3:C$8,,0,1)</f>
         <v>Saber</v>
@@ -10054,14 +10054,14 @@
       <c r="N13" s="70" t="s">
         <v>650</v>
       </c>
-      <c r="O13" s="79" t="s">
+      <c r="O13" s="76" t="s">
         <v>617</v>
       </c>
-      <c r="P13" s="84" t="s">
+      <c r="P13" s="82" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="14" spans="1:17" ht="66" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:17" ht="72" x14ac:dyDescent="0.3">
       <c r="A14" s="5" t="str">
         <f>_xlfn.XLOOKUP(B14,'Paso 3 Redacción RA '!I$3:I$8,'Paso 3 Redacción RA '!C$3:C$8,,0,1)</f>
         <v>Saberhacer</v>
@@ -10081,10 +10081,10 @@
       <c r="L14" s="74"/>
       <c r="M14" s="71"/>
       <c r="N14" s="71"/>
-      <c r="O14" s="80"/>
-      <c r="P14" s="85"/>
-    </row>
-    <row r="15" spans="1:17" ht="49.5" x14ac:dyDescent="0.35">
+      <c r="O14" s="77"/>
+      <c r="P14" s="83"/>
+    </row>
+    <row r="15" spans="1:17" ht="54" x14ac:dyDescent="0.3">
       <c r="A15" s="5" t="str">
         <f>_xlfn.XLOOKUP(B15,'Paso 3 Redacción RA '!I$3:I$8,'Paso 3 Redacción RA '!C$3:C$8,,0,1)</f>
         <v>Saberhacer</v>
@@ -10104,10 +10104,10 @@
       <c r="L15" s="74"/>
       <c r="M15" s="71"/>
       <c r="N15" s="71"/>
-      <c r="O15" s="80"/>
-      <c r="P15" s="85"/>
-    </row>
-    <row r="16" spans="1:17" ht="50" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="O15" s="77"/>
+      <c r="P15" s="83"/>
+    </row>
+    <row r="16" spans="1:17" ht="54.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A16" s="34" t="str">
         <f>_xlfn.XLOOKUP(B16,'Paso 3 Redacción RA '!I$3:I$8,'Paso 3 Redacción RA '!C$3:C$8,,0,1)</f>
         <v>Saberser</v>
@@ -10127,10 +10127,10 @@
       <c r="L16" s="75"/>
       <c r="M16" s="72"/>
       <c r="N16" s="72"/>
-      <c r="O16" s="88"/>
-      <c r="P16" s="92"/>
-    </row>
-    <row r="17" spans="1:17" ht="69" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="O16" s="78"/>
+      <c r="P16" s="84"/>
+    </row>
+    <row r="17" spans="1:17" ht="69" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="35" t="str">
         <f>_xlfn.XLOOKUP(B17,'Paso 3 Redacción RA '!I$3:I$8,'Paso 3 Redacción RA '!C$3:C$8,,0,1)</f>
         <v>Saber</v>
@@ -10154,7 +10154,7 @@
       <c r="H17" s="73" t="s">
         <v>595</v>
       </c>
-      <c r="I17" s="76">
+      <c r="I17" s="90">
         <v>2</v>
       </c>
       <c r="J17" s="73">
@@ -10169,20 +10169,20 @@
         <f>SUM(J17:K20)</f>
         <v>96</v>
       </c>
-      <c r="M17" s="81" t="s">
+      <c r="M17" s="79" t="s">
         <v>644</v>
       </c>
       <c r="N17" s="70" t="s">
         <v>650</v>
       </c>
-      <c r="O17" s="79" t="s">
+      <c r="O17" s="76" t="s">
         <v>617</v>
       </c>
       <c r="P17" s="70" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="18" spans="1:17" ht="66" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:17" ht="72" x14ac:dyDescent="0.3">
       <c r="A18" s="5" t="str">
         <f>_xlfn.XLOOKUP(B18,'Paso 3 Redacción RA '!I$3:I$8,'Paso 3 Redacción RA '!C$3:C$8,,0,1)</f>
         <v>Saberhacer</v>
@@ -10196,16 +10196,16 @@
       <c r="F18" s="68"/>
       <c r="G18" s="68"/>
       <c r="H18" s="74"/>
-      <c r="I18" s="77"/>
+      <c r="I18" s="91"/>
       <c r="J18" s="74"/>
       <c r="K18" s="74"/>
       <c r="L18" s="74"/>
-      <c r="M18" s="82"/>
+      <c r="M18" s="80"/>
       <c r="N18" s="71"/>
-      <c r="O18" s="80"/>
+      <c r="O18" s="77"/>
       <c r="P18" s="71"/>
     </row>
-    <row r="19" spans="1:17" ht="49.5" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:17" ht="54" x14ac:dyDescent="0.3">
       <c r="A19" s="5" t="str">
         <f>_xlfn.XLOOKUP(B19,'Paso 3 Redacción RA '!I$3:I$8,'Paso 3 Redacción RA '!C$3:C$8,,0,1)</f>
         <v>Saberhacer</v>
@@ -10219,16 +10219,16 @@
       <c r="F19" s="68"/>
       <c r="G19" s="68"/>
       <c r="H19" s="74"/>
-      <c r="I19" s="77"/>
+      <c r="I19" s="91"/>
       <c r="J19" s="74"/>
       <c r="K19" s="74"/>
       <c r="L19" s="74"/>
-      <c r="M19" s="82"/>
+      <c r="M19" s="80"/>
       <c r="N19" s="71"/>
-      <c r="O19" s="80"/>
+      <c r="O19" s="77"/>
       <c r="P19" s="71"/>
     </row>
-    <row r="20" spans="1:17" ht="50" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:17" ht="54.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A20" s="34" t="str">
         <f>_xlfn.XLOOKUP(B20,'Paso 3 Redacción RA '!I$3:I$8,'Paso 3 Redacción RA '!C$3:C$8,,0,1)</f>
         <v>Saberser</v>
@@ -10242,20 +10242,20 @@
       <c r="F20" s="69"/>
       <c r="G20" s="69"/>
       <c r="H20" s="75"/>
-      <c r="I20" s="78"/>
+      <c r="I20" s="92"/>
       <c r="J20" s="75"/>
       <c r="K20" s="75"/>
       <c r="L20" s="75"/>
-      <c r="M20" s="83"/>
+      <c r="M20" s="81"/>
       <c r="N20" s="72"/>
-      <c r="O20" s="88"/>
+      <c r="O20" s="78"/>
       <c r="P20" s="72"/>
       <c r="Q20" s="5">
         <f>SUM(I3:I20)</f>
         <v>11</v>
       </c>
     </row>
-    <row r="21" spans="1:17" ht="66" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:17" ht="72" x14ac:dyDescent="0.3">
       <c r="A21" s="5" t="str">
         <f>_xlfn.XLOOKUP(B21,'Paso 3 Redacción RA '!I$3:I$8,'Paso 3 Redacción RA '!C$3:C$8,,0,1)</f>
         <v>Saber</v>
@@ -10294,20 +10294,20 @@
         <f>SUM(J21:K23)</f>
         <v>96</v>
       </c>
-      <c r="M21" s="81" t="s">
+      <c r="M21" s="79" t="s">
         <v>647</v>
       </c>
       <c r="N21" s="70" t="s">
         <v>650</v>
       </c>
-      <c r="O21" s="79" t="s">
+      <c r="O21" s="76" t="s">
         <v>617</v>
       </c>
       <c r="P21" s="70" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="22" spans="1:17" ht="66" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:17" ht="72" x14ac:dyDescent="0.3">
       <c r="A22" s="5" t="str">
         <f>_xlfn.XLOOKUP(B22,'Paso 3 Redacción RA '!I$3:I$8,'Paso 3 Redacción RA '!C$3:C$8,,0,1)</f>
         <v>Saberhacer</v>
@@ -10325,12 +10325,12 @@
       <c r="J22" s="68"/>
       <c r="K22" s="68"/>
       <c r="L22" s="68"/>
-      <c r="M22" s="82"/>
+      <c r="M22" s="80"/>
       <c r="N22" s="71"/>
-      <c r="O22" s="80"/>
+      <c r="O22" s="77"/>
       <c r="P22" s="71"/>
     </row>
-    <row r="23" spans="1:17" ht="50" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:17" ht="54.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A23" s="5" t="str">
         <f>_xlfn.XLOOKUP(B23,'Paso 3 Redacción RA '!I$3:I$8,'Paso 3 Redacción RA '!C$3:C$8,,0,1)</f>
         <v>Saberhacer</v>
@@ -10348,12 +10348,12 @@
       <c r="J23" s="68"/>
       <c r="K23" s="68"/>
       <c r="L23" s="68"/>
-      <c r="M23" s="82"/>
+      <c r="M23" s="80"/>
       <c r="N23" s="71"/>
-      <c r="O23" s="80"/>
+      <c r="O23" s="77"/>
       <c r="P23" s="71"/>
     </row>
-    <row r="24" spans="1:17" ht="66" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:17" ht="72" x14ac:dyDescent="0.3">
       <c r="A24" s="35" t="str">
         <f>_xlfn.XLOOKUP(B24,'Paso 3 Redacción RA '!I$3:I$8,'Paso 3 Redacción RA '!C$3:C$8,,0,1)</f>
         <v>Saber</v>
@@ -10398,14 +10398,14 @@
       <c r="N24" s="70" t="s">
         <v>650</v>
       </c>
-      <c r="O24" s="79" t="s">
+      <c r="O24" s="76" t="s">
         <v>617</v>
       </c>
       <c r="P24" s="70" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="25" spans="1:17" ht="66" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:17" ht="72" x14ac:dyDescent="0.3">
       <c r="A25" s="5" t="str">
         <f>_xlfn.XLOOKUP(B25,'Paso 3 Redacción RA '!I$3:I$8,'Paso 3 Redacción RA '!C$3:C$8,,0,1)</f>
         <v>Saberhacer</v>
@@ -10425,10 +10425,10 @@
       <c r="L25" s="74"/>
       <c r="M25" s="71"/>
       <c r="N25" s="71"/>
-      <c r="O25" s="80"/>
+      <c r="O25" s="77"/>
       <c r="P25" s="71"/>
     </row>
-    <row r="26" spans="1:17" ht="50" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="26" spans="1:17" ht="54.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A26" s="34" t="str">
         <f>_xlfn.XLOOKUP(B26,'Paso 3 Redacción RA '!I$3:I$8,'Paso 3 Redacción RA '!C$3:C$8,,0,1)</f>
         <v>Saberser</v>
@@ -10448,12 +10448,12 @@
       <c r="L26" s="74"/>
       <c r="M26" s="71"/>
       <c r="N26" s="71"/>
-      <c r="O26" s="80"/>
+      <c r="O26" s="77"/>
       <c r="P26" s="71" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="27" spans="1:17" ht="66" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:17" ht="72" x14ac:dyDescent="0.3">
       <c r="A27" s="5" t="str">
         <f>_xlfn.XLOOKUP(B27,'Paso 3 Redacción RA '!I$3:I$8,'Paso 3 Redacción RA '!C$3:C$8,,0,1)</f>
         <v>Saber</v>
@@ -10492,20 +10492,20 @@
         <f>SUM(J27:K29)</f>
         <v>96</v>
       </c>
-      <c r="M27" s="81" t="s">
+      <c r="M27" s="79" t="s">
         <v>653</v>
       </c>
       <c r="N27" s="70" t="s">
         <v>650</v>
       </c>
-      <c r="O27" s="79" t="s">
+      <c r="O27" s="76" t="s">
         <v>617</v>
       </c>
       <c r="P27" s="70" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="28" spans="1:17" ht="66" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:17" ht="72" x14ac:dyDescent="0.3">
       <c r="A28" s="5" t="str">
         <f>_xlfn.XLOOKUP(B28,'Paso 3 Redacción RA '!I$3:I$8,'Paso 3 Redacción RA '!C$3:C$8,,0,1)</f>
         <v>Saberhacer</v>
@@ -10523,12 +10523,12 @@
       <c r="J28" s="74"/>
       <c r="K28" s="74"/>
       <c r="L28" s="74"/>
-      <c r="M28" s="82"/>
+      <c r="M28" s="80"/>
       <c r="N28" s="71"/>
-      <c r="O28" s="80"/>
+      <c r="O28" s="77"/>
       <c r="P28" s="71"/>
     </row>
-    <row r="29" spans="1:17" ht="50" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="29" spans="1:17" ht="54.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A29" s="5" t="str">
         <f>_xlfn.XLOOKUP(B29,'Paso 3 Redacción RA '!I$3:I$8,'Paso 3 Redacción RA '!C$3:C$8,,0,1)</f>
         <v>Saberser</v>
@@ -10546,12 +10546,12 @@
       <c r="J29" s="74"/>
       <c r="K29" s="74"/>
       <c r="L29" s="74"/>
-      <c r="M29" s="82"/>
+      <c r="M29" s="80"/>
       <c r="N29" s="71"/>
-      <c r="O29" s="80"/>
+      <c r="O29" s="77"/>
       <c r="P29" s="71"/>
     </row>
-    <row r="30" spans="1:17" ht="66" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:17" ht="72" x14ac:dyDescent="0.3">
       <c r="A30" s="35" t="str">
         <f>_xlfn.XLOOKUP(B30,'Paso 3 Redacción RA '!I$3:I$8,'Paso 3 Redacción RA '!C$3:C$8,,0,1)</f>
         <v>Saber</v>
@@ -10596,14 +10596,14 @@
       <c r="N30" s="70" t="s">
         <v>650</v>
       </c>
-      <c r="O30" s="79" t="s">
+      <c r="O30" s="76" t="s">
         <v>617</v>
       </c>
       <c r="P30" s="70" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="31" spans="1:17" ht="66" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:17" ht="72" x14ac:dyDescent="0.3">
       <c r="A31" s="5" t="str">
         <f>_xlfn.XLOOKUP(B31,'Paso 3 Redacción RA '!I$3:I$8,'Paso 3 Redacción RA '!C$3:C$8,,0,1)</f>
         <v>Saberhacer</v>
@@ -10623,10 +10623,10 @@
       <c r="L31" s="74"/>
       <c r="M31" s="71"/>
       <c r="N31" s="71"/>
-      <c r="O31" s="80"/>
+      <c r="O31" s="77"/>
       <c r="P31" s="71"/>
     </row>
-    <row r="32" spans="1:17" ht="50" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="32" spans="1:17" ht="54.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A32" s="5" t="str">
         <f>_xlfn.XLOOKUP(B32,'Paso 3 Redacción RA '!I$3:I$8,'Paso 3 Redacción RA '!C$3:C$8,,0,1)</f>
         <v>Saberser</v>
@@ -10646,10 +10646,10 @@
       <c r="L32" s="74"/>
       <c r="M32" s="71"/>
       <c r="N32" s="71"/>
-      <c r="O32" s="80"/>
+      <c r="O32" s="77"/>
       <c r="P32" s="71"/>
     </row>
-    <row r="33" spans="1:17" ht="69" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:17" ht="69" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="35" t="str">
         <f>_xlfn.XLOOKUP(B33,'Paso 3 Redacción RA '!I$3:I$8,'Paso 3 Redacción RA '!C$3:C$8,,0,1)</f>
         <v>Saber</v>
@@ -10688,7 +10688,7 @@
         <f>SUM(J33:K36)</f>
         <v>96</v>
       </c>
-      <c r="M33" s="81" t="s">
+      <c r="M33" s="79" t="s">
         <v>649</v>
       </c>
       <c r="N33" s="70" t="s">
@@ -10701,7 +10701,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="34" spans="1:17" ht="66" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:17" ht="72" x14ac:dyDescent="0.3">
       <c r="A34" s="5" t="str">
         <f>_xlfn.XLOOKUP(B34,'Paso 3 Redacción RA '!I$3:I$8,'Paso 3 Redacción RA '!C$3:C$8,,0,1)</f>
         <v>Saberhacer</v>
@@ -10719,12 +10719,12 @@
       <c r="J34" s="68"/>
       <c r="K34" s="68"/>
       <c r="L34" s="68"/>
-      <c r="M34" s="82"/>
+      <c r="M34" s="80"/>
       <c r="N34" s="71"/>
       <c r="O34" s="71"/>
       <c r="P34" s="71"/>
     </row>
-    <row r="35" spans="1:17" ht="49.5" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:17" ht="54" x14ac:dyDescent="0.3">
       <c r="A35" s="5" t="str">
         <f>_xlfn.XLOOKUP(B35,'Paso 3 Redacción RA '!I$3:I$8,'Paso 3 Redacción RA '!C$3:C$8,,0,1)</f>
         <v>Saberhacer</v>
@@ -10742,12 +10742,12 @@
       <c r="J35" s="68"/>
       <c r="K35" s="68"/>
       <c r="L35" s="68"/>
-      <c r="M35" s="82"/>
+      <c r="M35" s="80"/>
       <c r="N35" s="71"/>
       <c r="O35" s="71"/>
       <c r="P35" s="71"/>
     </row>
-    <row r="36" spans="1:17" ht="50" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="36" spans="1:17" ht="54.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A36" s="34" t="str">
         <f>_xlfn.XLOOKUP(B36,'Paso 3 Redacción RA '!I$3:I$8,'Paso 3 Redacción RA '!C$3:C$8,,0,1)</f>
         <v>Saberser</v>
@@ -10765,12 +10765,12 @@
       <c r="J36" s="69"/>
       <c r="K36" s="69"/>
       <c r="L36" s="69"/>
-      <c r="M36" s="83"/>
+      <c r="M36" s="81"/>
       <c r="N36" s="72"/>
       <c r="O36" s="72"/>
       <c r="P36" s="72"/>
     </row>
-    <row r="37" spans="1:17" ht="66" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:17" ht="72" x14ac:dyDescent="0.3">
       <c r="A37" s="35" t="str">
         <f>_xlfn.XLOOKUP(B37,'Paso 3 Redacción RA '!I$3:I$8,'Paso 3 Redacción RA '!C$3:C$8,,0,1)</f>
         <v>Saber</v>
@@ -10809,20 +10809,20 @@
         <f>SUM(J37:K37)</f>
         <v>144</v>
       </c>
-      <c r="M37" s="81" t="s">
+      <c r="M37" s="79" t="s">
         <v>643</v>
       </c>
       <c r="N37" s="70" t="s">
         <v>650</v>
       </c>
-      <c r="O37" s="79" t="s">
+      <c r="O37" s="76" t="s">
         <v>617</v>
       </c>
       <c r="P37" s="70" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="38" spans="1:17" ht="66" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:17" ht="72" x14ac:dyDescent="0.3">
       <c r="A38" s="5" t="str">
         <f>_xlfn.XLOOKUP(B38,'Paso 3 Redacción RA '!I$3:I$8,'Paso 3 Redacción RA '!C$3:C$8,,0,1)</f>
         <v>Saberhacer</v>
@@ -10840,12 +10840,12 @@
       <c r="J38" s="74"/>
       <c r="K38" s="74"/>
       <c r="L38" s="74"/>
-      <c r="M38" s="82"/>
+      <c r="M38" s="80"/>
       <c r="N38" s="71"/>
-      <c r="O38" s="80"/>
+      <c r="O38" s="77"/>
       <c r="P38" s="71"/>
     </row>
-    <row r="39" spans="1:17" ht="49.5" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:17" ht="54" x14ac:dyDescent="0.3">
       <c r="A39" s="5" t="str">
         <f>_xlfn.XLOOKUP(B39,'Paso 3 Redacción RA '!I$3:I$8,'Paso 3 Redacción RA '!C$3:C$8,,0,1)</f>
         <v>Saberhacer</v>
@@ -10863,12 +10863,12 @@
       <c r="J39" s="74"/>
       <c r="K39" s="74"/>
       <c r="L39" s="74"/>
-      <c r="M39" s="82"/>
+      <c r="M39" s="80"/>
       <c r="N39" s="71"/>
-      <c r="O39" s="80"/>
+      <c r="O39" s="77"/>
       <c r="P39" s="71"/>
     </row>
-    <row r="40" spans="1:17" ht="50" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="40" spans="1:17" ht="54.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A40" s="34" t="str">
         <f>_xlfn.XLOOKUP(B40,'Paso 3 Redacción RA '!I$3:I$8,'Paso 3 Redacción RA '!C$3:C$8,,0,1)</f>
         <v>Saberser</v>
@@ -10888,16 +10888,16 @@
       <c r="J40" s="75"/>
       <c r="K40" s="75"/>
       <c r="L40" s="75"/>
-      <c r="M40" s="83"/>
+      <c r="M40" s="81"/>
       <c r="N40" s="72"/>
-      <c r="O40" s="88"/>
+      <c r="O40" s="78"/>
       <c r="P40" s="72"/>
       <c r="Q40" s="5">
         <f>SUM(I21:I40)</f>
         <v>13</v>
       </c>
     </row>
-    <row r="41" spans="1:17" ht="39" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:17" ht="36" x14ac:dyDescent="0.3">
       <c r="C41" s="36" t="s">
         <v>105</v>
       </c>
@@ -10917,7 +10917,7 @@
         <v>Correcto: Cumple la Política de Gestión, Evaluación e Innovación Curricular</v>
       </c>
     </row>
-    <row r="42" spans="1:17" ht="39" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:17" ht="36" x14ac:dyDescent="0.3">
       <c r="H42" s="33" t="s">
         <v>107</v>
       </c>
@@ -10930,7 +10930,7 @@
         <v>Correcto: Cumple la Política de Gestión, Evaluación e Innovación Curricular</v>
       </c>
     </row>
-    <row r="43" spans="1:17" ht="39" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:17" ht="36" x14ac:dyDescent="0.3">
       <c r="H43" s="33" t="s">
         <v>108</v>
       </c>
@@ -10945,58 +10945,85 @@
     </row>
   </sheetData>
   <mergeCells count="155">
-    <mergeCell ref="C37:C40"/>
-    <mergeCell ref="D37:D40"/>
-    <mergeCell ref="E37:E40"/>
-    <mergeCell ref="F37:F40"/>
-    <mergeCell ref="G37:G40"/>
-    <mergeCell ref="H37:H40"/>
-    <mergeCell ref="I37:I40"/>
-    <mergeCell ref="J37:J40"/>
-    <mergeCell ref="K37:K40"/>
-    <mergeCell ref="O21:O23"/>
-    <mergeCell ref="P21:P23"/>
-    <mergeCell ref="O17:O20"/>
-    <mergeCell ref="P17:P20"/>
-    <mergeCell ref="N17:N20"/>
-    <mergeCell ref="O24:O26"/>
-    <mergeCell ref="P24:P26"/>
-    <mergeCell ref="L37:L40"/>
-    <mergeCell ref="M37:M40"/>
-    <mergeCell ref="N37:N40"/>
-    <mergeCell ref="O37:O40"/>
-    <mergeCell ref="P37:P40"/>
-    <mergeCell ref="L33:L36"/>
-    <mergeCell ref="M33:M36"/>
-    <mergeCell ref="N33:N36"/>
-    <mergeCell ref="O33:O36"/>
-    <mergeCell ref="P33:P36"/>
-    <mergeCell ref="P13:P16"/>
-    <mergeCell ref="O10:O12"/>
-    <mergeCell ref="P10:P12"/>
-    <mergeCell ref="P6:P9"/>
-    <mergeCell ref="P3:P5"/>
-    <mergeCell ref="N6:N9"/>
-    <mergeCell ref="M6:M9"/>
-    <mergeCell ref="O6:O9"/>
-    <mergeCell ref="O3:O5"/>
-    <mergeCell ref="C3:C5"/>
-    <mergeCell ref="D3:D5"/>
-    <mergeCell ref="E3:E5"/>
-    <mergeCell ref="G3:G5"/>
-    <mergeCell ref="H3:H5"/>
-    <mergeCell ref="I3:I5"/>
-    <mergeCell ref="N3:N5"/>
-    <mergeCell ref="M3:M5"/>
-    <mergeCell ref="L10:L12"/>
-    <mergeCell ref="M10:M12"/>
-    <mergeCell ref="J3:J5"/>
-    <mergeCell ref="K3:K5"/>
-    <mergeCell ref="L3:L5"/>
-    <mergeCell ref="J6:J9"/>
-    <mergeCell ref="K6:K9"/>
-    <mergeCell ref="F6:F9"/>
-    <mergeCell ref="F10:F12"/>
+    <mergeCell ref="C33:C36"/>
+    <mergeCell ref="D33:D36"/>
+    <mergeCell ref="E33:E36"/>
+    <mergeCell ref="F33:F36"/>
+    <mergeCell ref="G33:G36"/>
+    <mergeCell ref="H33:H36"/>
+    <mergeCell ref="I33:I36"/>
+    <mergeCell ref="J33:J36"/>
+    <mergeCell ref="K33:K36"/>
+    <mergeCell ref="C17:C20"/>
+    <mergeCell ref="D17:D20"/>
+    <mergeCell ref="E17:E20"/>
+    <mergeCell ref="G17:G20"/>
+    <mergeCell ref="H17:H20"/>
+    <mergeCell ref="I17:I20"/>
+    <mergeCell ref="J17:J20"/>
+    <mergeCell ref="K17:K20"/>
+    <mergeCell ref="C27:C29"/>
+    <mergeCell ref="D27:D29"/>
+    <mergeCell ref="E27:E29"/>
+    <mergeCell ref="G27:G29"/>
+    <mergeCell ref="H27:H29"/>
+    <mergeCell ref="I27:I29"/>
+    <mergeCell ref="J27:J29"/>
+    <mergeCell ref="K27:K29"/>
+    <mergeCell ref="C24:C26"/>
+    <mergeCell ref="D24:D26"/>
+    <mergeCell ref="E24:E26"/>
+    <mergeCell ref="F17:F20"/>
+    <mergeCell ref="F21:F23"/>
+    <mergeCell ref="F24:F26"/>
+    <mergeCell ref="F27:F29"/>
+    <mergeCell ref="D30:D32"/>
+    <mergeCell ref="I30:I32"/>
+    <mergeCell ref="P30:P32"/>
+    <mergeCell ref="O30:O32"/>
+    <mergeCell ref="N30:N32"/>
+    <mergeCell ref="C21:C23"/>
+    <mergeCell ref="D21:D23"/>
+    <mergeCell ref="E21:E23"/>
+    <mergeCell ref="G21:G23"/>
+    <mergeCell ref="H21:H23"/>
+    <mergeCell ref="I21:I23"/>
+    <mergeCell ref="J21:J23"/>
+    <mergeCell ref="K21:K23"/>
+    <mergeCell ref="L21:L23"/>
+    <mergeCell ref="M21:M23"/>
+    <mergeCell ref="N21:N23"/>
+    <mergeCell ref="C30:C32"/>
+    <mergeCell ref="N27:N29"/>
+    <mergeCell ref="O27:O29"/>
+    <mergeCell ref="P27:P29"/>
+    <mergeCell ref="N24:N26"/>
+    <mergeCell ref="G30:G32"/>
+    <mergeCell ref="H30:H32"/>
+    <mergeCell ref="M30:M32"/>
+    <mergeCell ref="E30:E32"/>
+    <mergeCell ref="M13:M16"/>
+    <mergeCell ref="L13:L16"/>
+    <mergeCell ref="K13:K16"/>
+    <mergeCell ref="J13:J16"/>
+    <mergeCell ref="I13:I16"/>
+    <mergeCell ref="H13:H16"/>
+    <mergeCell ref="L17:L20"/>
+    <mergeCell ref="M17:M20"/>
+    <mergeCell ref="M27:M29"/>
+    <mergeCell ref="K24:K26"/>
+    <mergeCell ref="L24:L26"/>
+    <mergeCell ref="L27:L29"/>
+    <mergeCell ref="F13:F16"/>
+    <mergeCell ref="F30:F32"/>
+    <mergeCell ref="L30:L32"/>
+    <mergeCell ref="K30:K32"/>
+    <mergeCell ref="J30:J32"/>
+    <mergeCell ref="G24:G26"/>
+    <mergeCell ref="H24:H26"/>
+    <mergeCell ref="I24:I26"/>
+    <mergeCell ref="J24:J26"/>
+    <mergeCell ref="M24:M26"/>
     <mergeCell ref="C13:C16"/>
     <mergeCell ref="D13:D16"/>
     <mergeCell ref="E13:E16"/>
@@ -11021,85 +11048,58 @@
     <mergeCell ref="K10:K12"/>
     <mergeCell ref="H6:H9"/>
     <mergeCell ref="I6:I9"/>
-    <mergeCell ref="E30:E32"/>
-    <mergeCell ref="M13:M16"/>
-    <mergeCell ref="L13:L16"/>
-    <mergeCell ref="K13:K16"/>
-    <mergeCell ref="J13:J16"/>
-    <mergeCell ref="I13:I16"/>
-    <mergeCell ref="H13:H16"/>
-    <mergeCell ref="L17:L20"/>
-    <mergeCell ref="M17:M20"/>
-    <mergeCell ref="M27:M29"/>
-    <mergeCell ref="K24:K26"/>
-    <mergeCell ref="L24:L26"/>
-    <mergeCell ref="L27:L29"/>
-    <mergeCell ref="F13:F16"/>
-    <mergeCell ref="F30:F32"/>
-    <mergeCell ref="L30:L32"/>
-    <mergeCell ref="K30:K32"/>
-    <mergeCell ref="J30:J32"/>
-    <mergeCell ref="G24:G26"/>
-    <mergeCell ref="H24:H26"/>
-    <mergeCell ref="I24:I26"/>
-    <mergeCell ref="J24:J26"/>
-    <mergeCell ref="M24:M26"/>
-    <mergeCell ref="D30:D32"/>
-    <mergeCell ref="I30:I32"/>
-    <mergeCell ref="P30:P32"/>
-    <mergeCell ref="O30:O32"/>
-    <mergeCell ref="N30:N32"/>
-    <mergeCell ref="C21:C23"/>
-    <mergeCell ref="D21:D23"/>
-    <mergeCell ref="E21:E23"/>
-    <mergeCell ref="G21:G23"/>
-    <mergeCell ref="H21:H23"/>
-    <mergeCell ref="I21:I23"/>
-    <mergeCell ref="J21:J23"/>
-    <mergeCell ref="K21:K23"/>
-    <mergeCell ref="L21:L23"/>
-    <mergeCell ref="M21:M23"/>
-    <mergeCell ref="N21:N23"/>
-    <mergeCell ref="C30:C32"/>
-    <mergeCell ref="N27:N29"/>
-    <mergeCell ref="O27:O29"/>
-    <mergeCell ref="P27:P29"/>
-    <mergeCell ref="N24:N26"/>
-    <mergeCell ref="G30:G32"/>
-    <mergeCell ref="H30:H32"/>
-    <mergeCell ref="M30:M32"/>
-    <mergeCell ref="C17:C20"/>
-    <mergeCell ref="D17:D20"/>
-    <mergeCell ref="E17:E20"/>
-    <mergeCell ref="G17:G20"/>
-    <mergeCell ref="H17:H20"/>
-    <mergeCell ref="I17:I20"/>
-    <mergeCell ref="J17:J20"/>
-    <mergeCell ref="K17:K20"/>
-    <mergeCell ref="C27:C29"/>
-    <mergeCell ref="D27:D29"/>
-    <mergeCell ref="E27:E29"/>
-    <mergeCell ref="G27:G29"/>
-    <mergeCell ref="H27:H29"/>
-    <mergeCell ref="I27:I29"/>
-    <mergeCell ref="J27:J29"/>
-    <mergeCell ref="K27:K29"/>
-    <mergeCell ref="C24:C26"/>
-    <mergeCell ref="D24:D26"/>
-    <mergeCell ref="E24:E26"/>
-    <mergeCell ref="F17:F20"/>
-    <mergeCell ref="F21:F23"/>
-    <mergeCell ref="F24:F26"/>
-    <mergeCell ref="F27:F29"/>
-    <mergeCell ref="C33:C36"/>
-    <mergeCell ref="D33:D36"/>
-    <mergeCell ref="E33:E36"/>
-    <mergeCell ref="F33:F36"/>
-    <mergeCell ref="G33:G36"/>
-    <mergeCell ref="H33:H36"/>
-    <mergeCell ref="I33:I36"/>
-    <mergeCell ref="J33:J36"/>
-    <mergeCell ref="K33:K36"/>
+    <mergeCell ref="C3:C5"/>
+    <mergeCell ref="D3:D5"/>
+    <mergeCell ref="E3:E5"/>
+    <mergeCell ref="G3:G5"/>
+    <mergeCell ref="H3:H5"/>
+    <mergeCell ref="I3:I5"/>
+    <mergeCell ref="N3:N5"/>
+    <mergeCell ref="M3:M5"/>
+    <mergeCell ref="L10:L12"/>
+    <mergeCell ref="M10:M12"/>
+    <mergeCell ref="J3:J5"/>
+    <mergeCell ref="K3:K5"/>
+    <mergeCell ref="L3:L5"/>
+    <mergeCell ref="J6:J9"/>
+    <mergeCell ref="K6:K9"/>
+    <mergeCell ref="F6:F9"/>
+    <mergeCell ref="F10:F12"/>
+    <mergeCell ref="P13:P16"/>
+    <mergeCell ref="O10:O12"/>
+    <mergeCell ref="P10:P12"/>
+    <mergeCell ref="P6:P9"/>
+    <mergeCell ref="P3:P5"/>
+    <mergeCell ref="N6:N9"/>
+    <mergeCell ref="M6:M9"/>
+    <mergeCell ref="O6:O9"/>
+    <mergeCell ref="O3:O5"/>
+    <mergeCell ref="O21:O23"/>
+    <mergeCell ref="P21:P23"/>
+    <mergeCell ref="O17:O20"/>
+    <mergeCell ref="P17:P20"/>
+    <mergeCell ref="N17:N20"/>
+    <mergeCell ref="O24:O26"/>
+    <mergeCell ref="P24:P26"/>
+    <mergeCell ref="L37:L40"/>
+    <mergeCell ref="M37:M40"/>
+    <mergeCell ref="N37:N40"/>
+    <mergeCell ref="O37:O40"/>
+    <mergeCell ref="P37:P40"/>
+    <mergeCell ref="L33:L36"/>
+    <mergeCell ref="M33:M36"/>
+    <mergeCell ref="N33:N36"/>
+    <mergeCell ref="O33:O36"/>
+    <mergeCell ref="P33:P36"/>
+    <mergeCell ref="C37:C40"/>
+    <mergeCell ref="D37:D40"/>
+    <mergeCell ref="E37:E40"/>
+    <mergeCell ref="F37:F40"/>
+    <mergeCell ref="G37:G40"/>
+    <mergeCell ref="H37:H40"/>
+    <mergeCell ref="I37:I40"/>
+    <mergeCell ref="J37:J40"/>
+    <mergeCell ref="K37:K40"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B3:B54" xr:uid="{149936BB-E9F7-467B-9B8A-466861C21273}">
@@ -11115,13 +11115,13 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8E64FCBD-ADC1-40F4-BFE8-98BA12AA9611}">
   <dimension ref="B1:D37"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.453125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="27.1796875" customWidth="1"/>
-    <col min="4" max="4" width="99.26953125" customWidth="1"/>
+    <col min="2" max="2" width="27.21875" customWidth="1"/>
+    <col min="4" max="4" width="99.21875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:4" ht="30.5" x14ac:dyDescent="0.5">
+    <row r="1" spans="2:4" ht="31.2" x14ac:dyDescent="0.5">
       <c r="B1" s="1" t="s">
         <v>109</v>
       </c>
@@ -11129,182 +11129,182 @@
         <v>110</v>
       </c>
     </row>
-    <row r="2" spans="2:4" ht="16.5" x14ac:dyDescent="0.5">
+    <row r="2" spans="2:4" ht="18" x14ac:dyDescent="0.5">
       <c r="B2" s="1" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="3" spans="2:4" ht="16.5" x14ac:dyDescent="0.5">
+    <row r="3" spans="2:4" ht="18" x14ac:dyDescent="0.5">
       <c r="B3" s="1" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="4" spans="2:4" ht="16.5" x14ac:dyDescent="0.5">
+    <row r="4" spans="2:4" ht="18" x14ac:dyDescent="0.5">
       <c r="B4" s="1" t="s">
         <v>113</v>
       </c>
     </row>
-    <row r="5" spans="2:4" ht="16.5" x14ac:dyDescent="0.5">
+    <row r="5" spans="2:4" ht="18" x14ac:dyDescent="0.5">
       <c r="B5" s="1" t="s">
         <v>114</v>
       </c>
     </row>
-    <row r="6" spans="2:4" ht="16.5" x14ac:dyDescent="0.5">
+    <row r="6" spans="2:4" ht="18" x14ac:dyDescent="0.5">
       <c r="B6" s="1" t="s">
         <v>115</v>
       </c>
     </row>
-    <row r="7" spans="2:4" ht="16.5" x14ac:dyDescent="0.5">
+    <row r="7" spans="2:4" ht="18" x14ac:dyDescent="0.5">
       <c r="B7" s="1" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="8" spans="2:4" ht="16.5" x14ac:dyDescent="0.5">
+    <row r="8" spans="2:4" ht="18" x14ac:dyDescent="0.5">
       <c r="B8" s="1" t="s">
         <v>117</v>
       </c>
     </row>
-    <row r="9" spans="2:4" ht="16.5" x14ac:dyDescent="0.5">
+    <row r="9" spans="2:4" ht="18" x14ac:dyDescent="0.5">
       <c r="B9" s="1" t="s">
         <v>118</v>
       </c>
     </row>
-    <row r="10" spans="2:4" ht="16.5" x14ac:dyDescent="0.5">
+    <row r="10" spans="2:4" ht="18" x14ac:dyDescent="0.5">
       <c r="B10" s="1" t="s">
         <v>119</v>
       </c>
     </row>
-    <row r="11" spans="2:4" ht="16.5" x14ac:dyDescent="0.5">
+    <row r="11" spans="2:4" ht="18" x14ac:dyDescent="0.5">
       <c r="B11" s="1" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="12" spans="2:4" ht="16.5" x14ac:dyDescent="0.5">
+    <row r="12" spans="2:4" ht="18" x14ac:dyDescent="0.5">
       <c r="B12" s="1" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="13" spans="2:4" ht="16.5" x14ac:dyDescent="0.5">
+    <row r="13" spans="2:4" ht="18" x14ac:dyDescent="0.5">
       <c r="B13" s="1" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="14" spans="2:4" ht="16.5" x14ac:dyDescent="0.5">
+    <row r="14" spans="2:4" ht="18" x14ac:dyDescent="0.5">
       <c r="B14" s="1" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="15" spans="2:4" ht="16.5" x14ac:dyDescent="0.5">
+    <row r="15" spans="2:4" ht="18" x14ac:dyDescent="0.5">
       <c r="B15" s="1" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="16" spans="2:4" ht="16.5" x14ac:dyDescent="0.5">
+    <row r="16" spans="2:4" ht="18" x14ac:dyDescent="0.5">
       <c r="B16" s="1" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="17" spans="2:2" ht="16.5" x14ac:dyDescent="0.5">
+    <row r="17" spans="2:2" ht="18" x14ac:dyDescent="0.5">
       <c r="B17" s="1" t="s">
         <v>126</v>
       </c>
     </row>
-    <row r="18" spans="2:2" ht="16.5" x14ac:dyDescent="0.5">
+    <row r="18" spans="2:2" ht="18" x14ac:dyDescent="0.5">
       <c r="B18" s="1" t="s">
         <v>127</v>
       </c>
     </row>
-    <row r="19" spans="2:2" ht="16.5" x14ac:dyDescent="0.5">
+    <row r="19" spans="2:2" ht="18" x14ac:dyDescent="0.5">
       <c r="B19" s="1" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="20" spans="2:2" ht="16.5" x14ac:dyDescent="0.5">
+    <row r="20" spans="2:2" ht="18" x14ac:dyDescent="0.5">
       <c r="B20" s="1" t="s">
         <v>129</v>
       </c>
     </row>
-    <row r="21" spans="2:2" ht="16.5" x14ac:dyDescent="0.5">
+    <row r="21" spans="2:2" ht="18" x14ac:dyDescent="0.5">
       <c r="B21" s="1" t="s">
         <v>130</v>
       </c>
     </row>
-    <row r="22" spans="2:2" ht="16.5" x14ac:dyDescent="0.5">
+    <row r="22" spans="2:2" ht="18" x14ac:dyDescent="0.5">
       <c r="B22" s="1" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="23" spans="2:2" ht="16.5" x14ac:dyDescent="0.5">
+    <row r="23" spans="2:2" ht="18" x14ac:dyDescent="0.5">
       <c r="B23" s="1" t="s">
         <v>132</v>
       </c>
     </row>
-    <row r="24" spans="2:2" ht="16.5" x14ac:dyDescent="0.5">
+    <row r="24" spans="2:2" ht="18" x14ac:dyDescent="0.5">
       <c r="B24" s="1" t="s">
         <v>133</v>
       </c>
     </row>
-    <row r="25" spans="2:2" ht="16.5" x14ac:dyDescent="0.5">
+    <row r="25" spans="2:2" ht="18" x14ac:dyDescent="0.5">
       <c r="B25" s="1" t="s">
         <v>134</v>
       </c>
     </row>
-    <row r="26" spans="2:2" ht="16.5" x14ac:dyDescent="0.5">
+    <row r="26" spans="2:2" ht="18" x14ac:dyDescent="0.5">
       <c r="B26" s="1" t="s">
         <v>135</v>
       </c>
     </row>
-    <row r="27" spans="2:2" ht="16.5" x14ac:dyDescent="0.5">
+    <row r="27" spans="2:2" ht="18" x14ac:dyDescent="0.5">
       <c r="B27" s="1" t="s">
         <v>136</v>
       </c>
     </row>
-    <row r="28" spans="2:2" ht="16.5" x14ac:dyDescent="0.5">
+    <row r="28" spans="2:2" ht="18" x14ac:dyDescent="0.5">
       <c r="B28" s="1" t="s">
         <v>137</v>
       </c>
     </row>
-    <row r="29" spans="2:2" ht="16.5" x14ac:dyDescent="0.5">
+    <row r="29" spans="2:2" ht="18" x14ac:dyDescent="0.5">
       <c r="B29" s="1" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="30" spans="2:2" ht="16.5" x14ac:dyDescent="0.5">
+    <row r="30" spans="2:2" ht="18" x14ac:dyDescent="0.5">
       <c r="B30" s="1" t="s">
         <v>139</v>
       </c>
     </row>
-    <row r="31" spans="2:2" ht="16.5" x14ac:dyDescent="0.5">
+    <row r="31" spans="2:2" ht="18" x14ac:dyDescent="0.5">
       <c r="B31" s="1" t="s">
         <v>140</v>
       </c>
     </row>
-    <row r="32" spans="2:2" ht="16.5" x14ac:dyDescent="0.5">
+    <row r="32" spans="2:2" ht="18" x14ac:dyDescent="0.5">
       <c r="B32" s="1" t="s">
         <v>141</v>
       </c>
     </row>
-    <row r="33" spans="2:2" ht="16.5" x14ac:dyDescent="0.5">
+    <row r="33" spans="2:2" ht="18" x14ac:dyDescent="0.5">
       <c r="B33" s="1" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="34" spans="2:2" ht="16.5" x14ac:dyDescent="0.5">
+    <row r="34" spans="2:2" ht="18" x14ac:dyDescent="0.5">
       <c r="B34" s="1" t="s">
         <v>143</v>
       </c>
     </row>
-    <row r="35" spans="2:2" ht="16.5" x14ac:dyDescent="0.5">
+    <row r="35" spans="2:2" ht="18" x14ac:dyDescent="0.5">
       <c r="B35" s="1" t="s">
         <v>144</v>
       </c>
     </row>
-    <row r="36" spans="2:2" ht="16.5" x14ac:dyDescent="0.5">
+    <row r="36" spans="2:2" ht="18" x14ac:dyDescent="0.5">
       <c r="B36" s="1" t="s">
         <v>145</v>
       </c>
     </row>
-    <row r="37" spans="2:2" ht="16.5" x14ac:dyDescent="0.5">
+    <row r="37" spans="2:2" ht="18" x14ac:dyDescent="0.5">
       <c r="B37" s="1" t="s">
         <v>146</v>
       </c>
@@ -11320,139 +11320,139 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{61A97597-49CE-4804-805A-84A20592BE98}">
   <dimension ref="A1:BK108"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.453125" defaultRowHeight="16.5" x14ac:dyDescent="0.5"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="18" x14ac:dyDescent="0.5"/>
   <cols>
-    <col min="1" max="1" width="20.453125" style="1" customWidth="1"/>
-    <col min="2" max="2" width="14.26953125" style="1" customWidth="1"/>
-    <col min="3" max="3" width="22.1796875" style="1" customWidth="1"/>
-    <col min="4" max="4" width="21.54296875" style="1" customWidth="1"/>
-    <col min="5" max="5" width="22.81640625" style="1" customWidth="1"/>
-    <col min="6" max="6" width="16.81640625" style="1" customWidth="1"/>
-    <col min="7" max="7" width="21.81640625" style="1" customWidth="1"/>
-    <col min="8" max="8" width="26.1796875" style="1" customWidth="1"/>
-    <col min="9" max="9" width="25.26953125" style="1" customWidth="1"/>
-    <col min="10" max="10" width="24.453125" style="1" customWidth="1"/>
-    <col min="11" max="11" width="15.26953125" style="1" customWidth="1"/>
-    <col min="12" max="17" width="17.7265625" style="1" customWidth="1"/>
-    <col min="18" max="18" width="22.54296875" style="1" customWidth="1"/>
-    <col min="19" max="33" width="17.453125" style="1" customWidth="1"/>
-    <col min="34" max="36" width="13.1796875" style="1" customWidth="1"/>
-    <col min="37" max="37" width="14.54296875" style="1" customWidth="1"/>
-    <col min="38" max="38" width="23.1796875" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="20.44140625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="14.21875" style="1" customWidth="1"/>
+    <col min="3" max="3" width="22.21875" style="1" customWidth="1"/>
+    <col min="4" max="4" width="21.5546875" style="1" customWidth="1"/>
+    <col min="5" max="5" width="22.77734375" style="1" customWidth="1"/>
+    <col min="6" max="6" width="16.77734375" style="1" customWidth="1"/>
+    <col min="7" max="7" width="21.77734375" style="1" customWidth="1"/>
+    <col min="8" max="8" width="26.21875" style="1" customWidth="1"/>
+    <col min="9" max="9" width="25.21875" style="1" customWidth="1"/>
+    <col min="10" max="10" width="24.44140625" style="1" customWidth="1"/>
+    <col min="11" max="11" width="15.21875" style="1" customWidth="1"/>
+    <col min="12" max="17" width="17.77734375" style="1" customWidth="1"/>
+    <col min="18" max="18" width="22.5546875" style="1" customWidth="1"/>
+    <col min="19" max="33" width="17.44140625" style="1" customWidth="1"/>
+    <col min="34" max="36" width="13.21875" style="1" customWidth="1"/>
+    <col min="37" max="37" width="14.5546875" style="1" customWidth="1"/>
+    <col min="38" max="38" width="23.21875" style="1" bestFit="1" customWidth="1"/>
     <col min="39" max="39" width="18" style="1" customWidth="1"/>
-    <col min="40" max="40" width="20.453125" style="1" bestFit="1" customWidth="1"/>
-    <col min="41" max="41" width="21.81640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="42" max="42" width="17.453125" style="1" bestFit="1" customWidth="1"/>
-    <col min="43" max="43" width="18.54296875" style="1" bestFit="1" customWidth="1"/>
-    <col min="44" max="44" width="16.7265625" style="1" customWidth="1"/>
-    <col min="45" max="45" width="26.54296875" style="1" bestFit="1" customWidth="1"/>
-    <col min="46" max="46" width="21.54296875" style="1" bestFit="1" customWidth="1"/>
-    <col min="47" max="47" width="19.1796875" style="1" bestFit="1" customWidth="1"/>
-    <col min="48" max="48" width="24.1796875" style="1" bestFit="1" customWidth="1"/>
-    <col min="49" max="49" width="24.81640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="50" max="50" width="23.1796875" style="1" bestFit="1" customWidth="1"/>
-    <col min="51" max="51" width="22.26953125" style="1" bestFit="1" customWidth="1"/>
-    <col min="52" max="52" width="32.1796875" style="1" bestFit="1" customWidth="1"/>
-    <col min="53" max="53" width="13.26953125" style="1" customWidth="1"/>
-    <col min="54" max="54" width="23.81640625" style="1" customWidth="1"/>
-    <col min="55" max="55" width="22.54296875" style="1" customWidth="1"/>
-    <col min="56" max="56" width="21.453125" style="1" customWidth="1"/>
+    <col min="40" max="40" width="20.44140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="41" max="41" width="21.77734375" style="1" bestFit="1" customWidth="1"/>
+    <col min="42" max="42" width="17.44140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="43" max="43" width="18.5546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="44" max="44" width="16.77734375" style="1" customWidth="1"/>
+    <col min="45" max="45" width="26.5546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="46" max="46" width="21.5546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="47" max="47" width="19.21875" style="1" bestFit="1" customWidth="1"/>
+    <col min="48" max="48" width="24.21875" style="1" bestFit="1" customWidth="1"/>
+    <col min="49" max="49" width="24.77734375" style="1" bestFit="1" customWidth="1"/>
+    <col min="50" max="50" width="23.21875" style="1" bestFit="1" customWidth="1"/>
+    <col min="51" max="51" width="22.21875" style="1" bestFit="1" customWidth="1"/>
+    <col min="52" max="52" width="32.21875" style="1" bestFit="1" customWidth="1"/>
+    <col min="53" max="53" width="13.21875" style="1" customWidth="1"/>
+    <col min="54" max="54" width="23.77734375" style="1" customWidth="1"/>
+    <col min="55" max="55" width="22.5546875" style="1" customWidth="1"/>
+    <col min="56" max="56" width="21.44140625" style="1" customWidth="1"/>
     <col min="57" max="57" width="25" style="1" customWidth="1"/>
-    <col min="58" max="58" width="24.7265625" style="1" customWidth="1"/>
-    <col min="59" max="59" width="22.7265625" style="1" customWidth="1"/>
-    <col min="60" max="63" width="13.26953125" style="1" customWidth="1"/>
-    <col min="64" max="16384" width="11.453125" style="1"/>
+    <col min="58" max="58" width="24.77734375" style="1" customWidth="1"/>
+    <col min="59" max="59" width="22.77734375" style="1" customWidth="1"/>
+    <col min="60" max="63" width="13.21875" style="1" customWidth="1"/>
+    <col min="64" max="16384" width="11.44140625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:63" x14ac:dyDescent="0.5">
-      <c r="S1" s="109" t="s">
+      <c r="S1" s="106" t="s">
         <v>147</v>
       </c>
-      <c r="T1" s="109"/>
-      <c r="U1" s="109"/>
-      <c r="V1" s="109"/>
-      <c r="W1" s="109"/>
-      <c r="X1" s="109"/>
-      <c r="Y1" s="109"/>
-      <c r="Z1" s="109"/>
-      <c r="AA1" s="109"/>
-      <c r="AB1" s="109"/>
-      <c r="AC1" s="109"/>
-      <c r="AD1" s="109"/>
-      <c r="AE1" s="109"/>
-      <c r="AF1" s="109"/>
-      <c r="AG1" s="109"/>
+      <c r="T1" s="106"/>
+      <c r="U1" s="106"/>
+      <c r="V1" s="106"/>
+      <c r="W1" s="106"/>
+      <c r="X1" s="106"/>
+      <c r="Y1" s="106"/>
+      <c r="Z1" s="106"/>
+      <c r="AA1" s="106"/>
+      <c r="AB1" s="106"/>
+      <c r="AC1" s="106"/>
+      <c r="AD1" s="106"/>
+      <c r="AE1" s="106"/>
+      <c r="AF1" s="106"/>
+      <c r="AG1" s="106"/>
       <c r="AH1" s="9"/>
       <c r="AI1" s="9"/>
       <c r="AJ1" s="9"/>
-      <c r="AL1" s="109" t="s">
+      <c r="AL1" s="106" t="s">
         <v>148</v>
       </c>
-      <c r="AM1" s="109"/>
-      <c r="AN1" s="109"/>
-      <c r="AO1" s="109"/>
-      <c r="AP1" s="109"/>
-      <c r="AQ1" s="109"/>
-      <c r="AR1" s="109"/>
-      <c r="AS1" s="109"/>
-      <c r="AT1" s="109"/>
-      <c r="AU1" s="109"/>
-      <c r="AV1" s="109"/>
-      <c r="AW1" s="109"/>
-      <c r="AX1" s="109"/>
-      <c r="AY1" s="109"/>
-      <c r="AZ1" s="109"/>
+      <c r="AM1" s="106"/>
+      <c r="AN1" s="106"/>
+      <c r="AO1" s="106"/>
+      <c r="AP1" s="106"/>
+      <c r="AQ1" s="106"/>
+      <c r="AR1" s="106"/>
+      <c r="AS1" s="106"/>
+      <c r="AT1" s="106"/>
+      <c r="AU1" s="106"/>
+      <c r="AV1" s="106"/>
+      <c r="AW1" s="106"/>
+      <c r="AX1" s="106"/>
+      <c r="AY1" s="106"/>
+      <c r="AZ1" s="106"/>
       <c r="BA1" s="9"/>
-      <c r="BB1" s="109" t="s">
+      <c r="BB1" s="106" t="s">
         <v>149</v>
       </c>
-      <c r="BC1" s="109"/>
-      <c r="BD1" s="109"/>
-      <c r="BE1" s="109"/>
-      <c r="BF1" s="109"/>
-      <c r="BG1" s="109"/>
+      <c r="BC1" s="106"/>
+      <c r="BD1" s="106"/>
+      <c r="BE1" s="106"/>
+      <c r="BF1" s="106"/>
+      <c r="BG1" s="106"/>
       <c r="BH1" s="9"/>
       <c r="BK1" s="9"/>
     </row>
     <row r="2" spans="1:63" x14ac:dyDescent="0.5">
-      <c r="L2" s="109" t="s">
+      <c r="L2" s="106" t="s">
         <v>150</v>
       </c>
-      <c r="M2" s="109"/>
-      <c r="N2" s="109"/>
-      <c r="O2" s="109"/>
-      <c r="P2" s="109"/>
-      <c r="Q2" s="109"/>
-      <c r="S2" s="110" t="s">
+      <c r="M2" s="106"/>
+      <c r="N2" s="106"/>
+      <c r="O2" s="106"/>
+      <c r="P2" s="106"/>
+      <c r="Q2" s="106"/>
+      <c r="S2" s="107" t="s">
         <v>151</v>
       </c>
-      <c r="T2" s="110"/>
-      <c r="U2" s="110"/>
-      <c r="V2" s="110"/>
-      <c r="W2" s="110"/>
-      <c r="X2" s="110"/>
-      <c r="Y2" s="110" t="s">
+      <c r="T2" s="107"/>
+      <c r="U2" s="107"/>
+      <c r="V2" s="107"/>
+      <c r="W2" s="107"/>
+      <c r="X2" s="107"/>
+      <c r="Y2" s="107" t="s">
         <v>152</v>
       </c>
-      <c r="Z2" s="110"/>
-      <c r="AA2" s="110"/>
-      <c r="AB2" s="110"/>
-      <c r="AC2" s="110" t="s">
+      <c r="Z2" s="107"/>
+      <c r="AA2" s="107"/>
+      <c r="AB2" s="107"/>
+      <c r="AC2" s="107" t="s">
         <v>153</v>
       </c>
-      <c r="AD2" s="110"/>
-      <c r="AE2" s="110"/>
-      <c r="AF2" s="110"/>
-      <c r="AG2" s="110"/>
+      <c r="AD2" s="107"/>
+      <c r="AE2" s="107"/>
+      <c r="AF2" s="107"/>
+      <c r="AG2" s="107"/>
       <c r="AH2" s="9"/>
       <c r="AI2" s="9"/>
       <c r="AJ2" s="9"/>
-      <c r="AL2" s="109"/>
-      <c r="AM2" s="109"/>
-      <c r="AN2" s="109"/>
-      <c r="AO2" s="109"/>
-      <c r="AP2" s="109"/>
-      <c r="AQ2" s="109"/>
+      <c r="AL2" s="106"/>
+      <c r="AM2" s="106"/>
+      <c r="AN2" s="106"/>
+      <c r="AO2" s="106"/>
+      <c r="AP2" s="106"/>
+      <c r="AQ2" s="106"/>
       <c r="AR2" s="9"/>
       <c r="AS2" s="9"/>
       <c r="AT2" s="9"/>
@@ -11557,29 +11557,29 @@
       <c r="AG3" s="1" t="s">
         <v>181</v>
       </c>
-      <c r="AL3" s="106" t="s">
+      <c r="AL3" s="108" t="s">
         <v>182</v>
       </c>
-      <c r="AM3" s="107"/>
-      <c r="AN3" s="107"/>
-      <c r="AO3" s="106" t="s">
+      <c r="AM3" s="109"/>
+      <c r="AN3" s="109"/>
+      <c r="AO3" s="108" t="s">
         <v>183</v>
       </c>
-      <c r="AP3" s="107"/>
-      <c r="AQ3" s="107"/>
-      <c r="AR3" s="106" t="s">
+      <c r="AP3" s="109"/>
+      <c r="AQ3" s="109"/>
+      <c r="AR3" s="108" t="s">
         <v>184</v>
       </c>
-      <c r="AS3" s="107"/>
-      <c r="AT3" s="107"/>
-      <c r="AU3" s="108"/>
-      <c r="AV3" s="106" t="s">
+      <c r="AS3" s="109"/>
+      <c r="AT3" s="109"/>
+      <c r="AU3" s="110"/>
+      <c r="AV3" s="108" t="s">
         <v>185</v>
       </c>
-      <c r="AW3" s="107"/>
-      <c r="AX3" s="107"/>
-      <c r="AY3" s="107"/>
-      <c r="AZ3" s="108"/>
+      <c r="AW3" s="109"/>
+      <c r="AX3" s="109"/>
+      <c r="AY3" s="109"/>
+      <c r="AZ3" s="110"/>
       <c r="BA3" s="10"/>
       <c r="BB3" s="10"/>
       <c r="BC3" s="10"/>
@@ -17646,11 +17646,6 @@
     <sortCondition ref="BC5:BC66"/>
   </sortState>
   <mergeCells count="12">
-    <mergeCell ref="S1:AG1"/>
-    <mergeCell ref="L2:Q2"/>
-    <mergeCell ref="S2:X2"/>
-    <mergeCell ref="Y2:AB2"/>
-    <mergeCell ref="AC2:AG2"/>
     <mergeCell ref="AV3:AZ3"/>
     <mergeCell ref="AR3:AU3"/>
     <mergeCell ref="AL3:AN3"/>
@@ -17658,6 +17653,11 @@
     <mergeCell ref="BB1:BG1"/>
     <mergeCell ref="AL2:AQ2"/>
     <mergeCell ref="AL1:AZ1"/>
+    <mergeCell ref="S1:AG1"/>
+    <mergeCell ref="L2:Q2"/>
+    <mergeCell ref="S2:X2"/>
+    <mergeCell ref="Y2:AB2"/>
+    <mergeCell ref="AC2:AG2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
